--- a/assets/constructions/examples/ctd_mib_gears.xlsx
+++ b/assets/constructions/examples/ctd_mib_gears.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,11 +569,31 @@
           <t>dbc2</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GMGS4SD205-075-4U</t>
+          <t>GMGS6ND80-27-5U</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -589,10 +609,10 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>52.07</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>19.05</v>
+        <v>27</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -600,20 +620,20 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>39.88</v>
+        <v>65.7</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -633,22 +653,36 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx019.05</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>VARGUS_1/2U_GM</t>
+          <t>VARGUS_5/8U_GM</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021 / NPA 56 Gear_Milling_Expanded Line INCH.pdf</t>
+          <t>2022/VARGUS Обработка шлицев и зубчатых колёс</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>791.9400000000001</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>69597.75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -729,11 +763,25 @@
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>791.9400000000001</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>69597.75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GMGS5SD80-27-5UT</t>
+          <t>GMGS3SD60-22-5U</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -749,10 +797,10 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -760,27 +808,27 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>55</v>
+        <v>45.6</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L4" t="n">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>4UT</t>
+          <t>4U</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -793,12 +841,12 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx027</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>VARGUS_5/8UT_GM</t>
+          <t>VARGUS_5/8U_GM</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -809,11 +857,25 @@
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>663.61</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>58319.77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GMGS6SD85-27-4UT</t>
+          <t>GMGS5SD315-100-5UT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -829,10 +891,10 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>25.4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -840,27 +902,27 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>66.5</v>
+        <v>55.12</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>9.9</v>
+        <v>12.7</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2UT</t>
+          <t>5UT</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -873,27 +935,41 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx027</t>
+          <t>ISO_6462:FDAxx025.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>VARGUS_1/2UT_GM</t>
+          <t>VARGUS_5/8UT_GM</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022/VARGUS Обработка шлицев и зубчатых колёс</t>
+          <t>2021 / NPA 56 Gear_Milling_Expanded Line INCH.pdf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>851.62</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>74842.58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GMGS6SD335-100-4UT</t>
+          <t>GMGS6SD85-27-4UT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -909,10 +985,10 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>85.09</v>
+        <v>85</v>
       </c>
       <c r="G6" t="n">
-        <v>25.4</v>
+        <v>27</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -920,7 +996,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>66.55</v>
+        <v>66.5</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
@@ -940,7 +1016,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>4UT</t>
+          <t>2UT</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -953,7 +1029,7 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx025.4</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -965,10 +1041,24 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021 / NPA 56 Gear_Milling_Expanded Line INCH.pdf</t>
+          <t>2022/VARGUS Обработка шлицев и зубчатых колёс</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>715.13</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>62847.48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
